--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>91322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R2" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>91318</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R3" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B2" t="n">
-        <v>91322</v>
+        <v>91546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R2" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R3" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488916</v>
+        <v>129487230</v>
       </c>
       <c r="B2" t="n">
-        <v>91546</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473088</v>
+        <v>473259</v>
       </c>
       <c r="R2" t="n">
-        <v>6990992</v>
+        <v>6991004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>91323</v>
+        <v>91546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R3" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129487230</v>
+        <v>129488870</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>91323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473259</v>
+        <v>473103</v>
       </c>
       <c r="R4" t="n">
-        <v>6991004</v>
+        <v>6991022</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1535,49 +1535,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R10" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,12 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,54 +1651,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R11" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1725,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1735,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129487230</v>
+        <v>129488916</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473259</v>
+        <v>473088</v>
       </c>
       <c r="R2" t="n">
-        <v>6991004</v>
+        <v>6990992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B3" t="n">
-        <v>91546</v>
+        <v>91326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R3" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488870</v>
+        <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>91323</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473103</v>
+        <v>473259</v>
       </c>
       <c r="R4" t="n">
-        <v>6991022</v>
+        <v>6991004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129488344</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R2" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488870</v>
+        <v>129487230</v>
       </c>
       <c r="B3" t="n">
-        <v>91326</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473103</v>
+        <v>473259</v>
       </c>
       <c r="R3" t="n">
-        <v>6991022</v>
+        <v>6991004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129487230</v>
+        <v>129488916</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473259</v>
+        <v>473088</v>
       </c>
       <c r="R4" t="n">
-        <v>6991004</v>
+        <v>6990992</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R2" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,49 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129487230</v>
+        <v>129488870</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>91326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473259</v>
+        <v>473103</v>
       </c>
       <c r="R3" t="n">
-        <v>6991004</v>
+        <v>6991022</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488916</v>
+        <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473088</v>
+        <v>473259</v>
       </c>
       <c r="R4" t="n">
-        <v>6990992</v>
+        <v>6991004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1535,54 +1535,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R10" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1624,7 +1619,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,49 +1651,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R11" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1735,12 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488870</v>
+        <v>129487230</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473103</v>
+        <v>473259</v>
       </c>
       <c r="R2" t="n">
-        <v>6991022</v>
+        <v>6991004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,49 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129487230</v>
+        <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473259</v>
+        <v>473088</v>
       </c>
       <c r="R3" t="n">
-        <v>6991004</v>
+        <v>6990992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,32 +893,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>91326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R4" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1535,49 +1535,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R10" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,12 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,54 +1651,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R11" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1725,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1735,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129487230</v>
+        <v>129488870</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>91326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473259</v>
+        <v>473103</v>
       </c>
       <c r="R2" t="n">
-        <v>6991004</v>
+        <v>6991022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,45 +782,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488916</v>
+        <v>129487230</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473088</v>
+        <v>473259</v>
       </c>
       <c r="R3" t="n">
-        <v>6990992</v>
+        <v>6991004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,32 +893,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B4" t="n">
-        <v>91326</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R4" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1535,54 +1535,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R10" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1624,7 +1619,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,49 +1651,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R11" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1735,12 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>91577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R2" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,49 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129487230</v>
+        <v>129488870</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>91354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473259</v>
+        <v>473103</v>
       </c>
       <c r="R3" t="n">
-        <v>6991004</v>
+        <v>6991022</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488916</v>
+        <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473088</v>
+        <v>473259</v>
       </c>
       <c r="R4" t="n">
-        <v>6990992</v>
+        <v>6991004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,49 +1535,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R10" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,12 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,54 +1651,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R11" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1725,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1735,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488916</v>
+        <v>129487230</v>
       </c>
       <c r="B2" t="n">
-        <v>91577</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473088</v>
+        <v>473259</v>
       </c>
       <c r="R2" t="n">
-        <v>6990992</v>
+        <v>6991004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>91354</v>
+        <v>91577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R3" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129487230</v>
+        <v>129488870</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>91354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473259</v>
+        <v>473103</v>
       </c>
       <c r="R4" t="n">
-        <v>6991004</v>
+        <v>6991022</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1535,54 +1535,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R10" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1624,7 +1619,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,49 +1651,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R11" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1735,12 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129487230</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>129488870</v>
       </c>
       <c r="B4" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129488378</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,6 +1871,1203 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129762635</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>473156</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6990959</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129762559</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92305</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>473216</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6991032</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I en stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129762637</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>473119</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6990938</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129762560</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92305</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>473100</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6990917</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129762625</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>473178</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6990958</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129762636</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>473139</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6990943</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I en granstubbe.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129762561</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92305</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>473144</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6991057</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I en stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129762638</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>473089</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6990979</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I 2 stående döda granar som står nära varann.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129762621</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>473224</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6991014</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst  22 plantor och 1 vinterståndare inom ca 1 m2 yta i gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129487230</v>
+        <v>129488870</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>91361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473259</v>
+        <v>473103</v>
       </c>
       <c r="R2" t="n">
-        <v>6991004</v>
+        <v>6991022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +785,7 @@
         <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488870</v>
+        <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473103</v>
+        <v>473259</v>
       </c>
       <c r="R4" t="n">
-        <v>6991022</v>
+        <v>6991004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129488378</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>129762635</v>
       </c>
       <c r="B13" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129762559</v>
       </c>
       <c r="B14" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,41 +2144,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129762637</v>
+        <v>129762560</v>
       </c>
       <c r="B15" t="n">
-        <v>91583</v>
+        <v>92306</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2186,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473119</v>
+        <v>473100</v>
       </c>
       <c r="R15" t="n">
-        <v>6990938</v>
+        <v>6990917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,7 +2222,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,37 +2275,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762560</v>
+        <v>129762637</v>
       </c>
       <c r="B16" t="n">
-        <v>92305</v>
+        <v>91584</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473100</v>
+        <v>473119</v>
       </c>
       <c r="R16" t="n">
-        <v>6990917</v>
+        <v>6990938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran i gammal granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,7 +2413,7 @@
         <v>129762625</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129762636</v>
       </c>
       <c r="B18" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129762561</v>
       </c>
       <c r="B19" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>129762638</v>
       </c>
       <c r="B20" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>129762621</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B2" t="n">
-        <v>91361</v>
+        <v>91584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R2" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B3" t="n">
-        <v>91584</v>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R3" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762636</v>
+        <v>129762561</v>
       </c>
       <c r="B18" t="n">
-        <v>91584</v>
+        <v>92306</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473139</v>
+        <v>473144</v>
       </c>
       <c r="R18" t="n">
-        <v>6990943</v>
+        <v>6991057</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I en granstubbe.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2673,32 +2673,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762561</v>
+        <v>129762636</v>
       </c>
       <c r="B19" t="n">
-        <v>92306</v>
+        <v>91584</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473144</v>
+        <v>473139</v>
       </c>
       <c r="R19" t="n">
-        <v>6991057</v>
+        <v>6990943</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>I en granstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129488916</v>
       </c>
       <c r="B2" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129488870</v>
       </c>
       <c r="B3" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>129762635</v>
       </c>
       <c r="B13" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129762559</v>
       </c>
       <c r="B14" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129762560</v>
       </c>
       <c r="B15" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>129762637</v>
       </c>
       <c r="B16" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>129762625</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,32 +2538,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762561</v>
+        <v>129762636</v>
       </c>
       <c r="B18" t="n">
-        <v>92306</v>
+        <v>91589</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473144</v>
+        <v>473139</v>
       </c>
       <c r="R18" t="n">
-        <v>6991057</v>
+        <v>6990943</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>I en granstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2673,32 +2673,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762636</v>
+        <v>129762561</v>
       </c>
       <c r="B19" t="n">
-        <v>91584</v>
+        <v>92311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473139</v>
+        <v>473144</v>
       </c>
       <c r="R19" t="n">
-        <v>6990943</v>
+        <v>6991057</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I en granstubbe.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
         <v>129762638</v>
       </c>
       <c r="B20" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>129762621</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B2" t="n">
-        <v>91589</v>
+        <v>91366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R2" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>91366</v>
+        <v>91589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R3" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1535,49 +1535,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R10" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,12 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,54 +1651,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R11" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1725,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1735,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2144,37 +2144,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129762560</v>
+        <v>129762637</v>
       </c>
       <c r="B15" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2182,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473100</v>
+        <v>473119</v>
       </c>
       <c r="R15" t="n">
-        <v>6990917</v>
+        <v>6990938</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2226,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran i gammal granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,41 +2279,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762637</v>
+        <v>129762560</v>
       </c>
       <c r="B16" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473119</v>
+        <v>473100</v>
       </c>
       <c r="R16" t="n">
-        <v>6990938</v>
+        <v>6990917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762636</v>
+        <v>129762561</v>
       </c>
       <c r="B18" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473139</v>
+        <v>473144</v>
       </c>
       <c r="R18" t="n">
-        <v>6990943</v>
+        <v>6991057</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I en granstubbe.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2673,32 +2673,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762561</v>
+        <v>129762636</v>
       </c>
       <c r="B19" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473144</v>
+        <v>473139</v>
       </c>
       <c r="R19" t="n">
-        <v>6991057</v>
+        <v>6990943</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>I en granstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B2" t="n">
-        <v>91366</v>
+        <v>91589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R2" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B3" t="n">
-        <v>91589</v>
+        <v>91366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R3" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1535,54 +1535,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R10" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1624,7 +1619,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,49 +1651,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R11" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1735,12 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2144,41 +2144,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129762637</v>
+        <v>129762560</v>
       </c>
       <c r="B15" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2186,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473119</v>
+        <v>473100</v>
       </c>
       <c r="R15" t="n">
-        <v>6990938</v>
+        <v>6990917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,7 +2222,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,37 +2275,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762560</v>
+        <v>129762637</v>
       </c>
       <c r="B16" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473100</v>
+        <v>473119</v>
       </c>
       <c r="R16" t="n">
-        <v>6990917</v>
+        <v>6990938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran i gammal granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762561</v>
+        <v>129762636</v>
       </c>
       <c r="B18" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473144</v>
+        <v>473139</v>
       </c>
       <c r="R18" t="n">
-        <v>6991057</v>
+        <v>6990943</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>I en granstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2673,32 +2673,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762636</v>
+        <v>129762561</v>
       </c>
       <c r="B19" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473139</v>
+        <v>473144</v>
       </c>
       <c r="R19" t="n">
-        <v>6990943</v>
+        <v>6991057</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I en granstubbe.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B2" t="n">
-        <v>91589</v>
+        <v>91366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R2" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488870</v>
+        <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>91366</v>
+        <v>91589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473103</v>
+        <v>473088</v>
       </c>
       <c r="R3" t="n">
-        <v>6991022</v>
+        <v>6990992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488870</v>
+        <v>129487230</v>
       </c>
       <c r="B2" t="n">
-        <v>91366</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473103</v>
+        <v>473259</v>
       </c>
       <c r="R2" t="n">
-        <v>6991022</v>
+        <v>6991004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +789,7 @@
         <v>129488916</v>
       </c>
       <c r="B3" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,49 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129487230</v>
+        <v>129488870</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473259</v>
+        <v>473103</v>
       </c>
       <c r="R4" t="n">
-        <v>6991004</v>
+        <v>6991022</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>129762635</v>
       </c>
       <c r="B13" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129762559</v>
       </c>
       <c r="B14" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,37 +2144,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129762560</v>
+        <v>129762637</v>
       </c>
       <c r="B15" t="n">
-        <v>92311</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2182,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473100</v>
+        <v>473119</v>
       </c>
       <c r="R15" t="n">
-        <v>6990917</v>
+        <v>6990938</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2226,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran i gammal granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,41 +2279,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762637</v>
+        <v>129762560</v>
       </c>
       <c r="B16" t="n">
-        <v>91589</v>
+        <v>92315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473119</v>
+        <v>473100</v>
       </c>
       <c r="R16" t="n">
-        <v>6990938</v>
+        <v>6990917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,7 +2413,7 @@
         <v>129762625</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129762636</v>
       </c>
       <c r="B18" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129762561</v>
       </c>
       <c r="B19" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>129762638</v>
       </c>
       <c r="B20" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>129762621</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129487230</v>
+        <v>129488916</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>91595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473259</v>
+        <v>473088</v>
       </c>
       <c r="R2" t="n">
-        <v>6991004</v>
+        <v>6990992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488916</v>
+        <v>129488870</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>91372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473088</v>
+        <v>473103</v>
       </c>
       <c r="R3" t="n">
-        <v>6990992</v>
+        <v>6991022</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,45 +889,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129488870</v>
+        <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473103</v>
+        <v>473259</v>
       </c>
       <c r="R4" t="n">
-        <v>6991022</v>
+        <v>6991004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1003,7 @@
         <v>129487778</v>
       </c>
       <c r="B5" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129486912</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>129488424</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>129487063</v>
       </c>
       <c r="B9" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129488344</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129488640</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>129762635</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129762559</v>
       </c>
       <c r="B14" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129762637</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>129762560</v>
       </c>
       <c r="B16" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>129762625</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129762636</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129762561</v>
       </c>
       <c r="B19" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>129762638</v>
       </c>
       <c r="B20" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>129762621</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -2144,41 +2144,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129762637</v>
+        <v>129762560</v>
       </c>
       <c r="B15" t="n">
-        <v>91595</v>
+        <v>92317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2186,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473119</v>
+        <v>473100</v>
       </c>
       <c r="R15" t="n">
-        <v>6990938</v>
+        <v>6990917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,7 +2222,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,37 +2275,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762560</v>
+        <v>129762637</v>
       </c>
       <c r="B16" t="n">
-        <v>92317</v>
+        <v>91595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473100</v>
+        <v>473119</v>
       </c>
       <c r="R16" t="n">
-        <v>6990917</v>
+        <v>6990938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran i gammal granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -2538,32 +2538,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762636</v>
+        <v>129762561</v>
       </c>
       <c r="B18" t="n">
-        <v>91595</v>
+        <v>92317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473139</v>
+        <v>473144</v>
       </c>
       <c r="R18" t="n">
-        <v>6990943</v>
+        <v>6991057</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I en granstubbe.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2673,32 +2673,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762561</v>
+        <v>129762636</v>
       </c>
       <c r="B19" t="n">
-        <v>92317</v>
+        <v>91595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473144</v>
+        <v>473139</v>
       </c>
       <c r="R19" t="n">
-        <v>6991057</v>
+        <v>6990943</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>I en granstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129487230</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129487135</v>
       </c>
       <c r="B7" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1535,49 +1535,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488378</v>
+        <v>129488344</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473156</v>
+        <v>473159</v>
       </c>
       <c r="R10" t="n">
-        <v>6991029</v>
+        <v>6991024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1614,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,12 +1624,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,54 +1651,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488344</v>
+        <v>129488378</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473159</v>
+        <v>473156</v>
       </c>
       <c r="R11" t="n">
-        <v>6991024</v>
+        <v>6991029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1725,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1735,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2413,7 +2413,7 @@
         <v>129762625</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,32 +2538,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762561</v>
+        <v>129762636</v>
       </c>
       <c r="B18" t="n">
-        <v>92317</v>
+        <v>91595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473144</v>
+        <v>473139</v>
       </c>
       <c r="R18" t="n">
-        <v>6991057</v>
+        <v>6990943</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>I en granstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2673,32 +2673,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762636</v>
+        <v>129762561</v>
       </c>
       <c r="B19" t="n">
-        <v>91595</v>
+        <v>92317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473139</v>
+        <v>473144</v>
       </c>
       <c r="R19" t="n">
-        <v>6990943</v>
+        <v>6991057</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I en granstubbe.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
         <v>129762621</v>
       </c>
       <c r="B21" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>129762635</v>
       </c>
       <c r="B13" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129762559</v>
       </c>
       <c r="B14" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,37 +2144,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129762560</v>
+        <v>129762637</v>
       </c>
       <c r="B15" t="n">
-        <v>92317</v>
+        <v>91598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2182,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473100</v>
+        <v>473119</v>
       </c>
       <c r="R15" t="n">
-        <v>6990917</v>
+        <v>6990938</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2226,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran i gammal granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,41 +2279,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762637</v>
+        <v>129762560</v>
       </c>
       <c r="B16" t="n">
-        <v>91595</v>
+        <v>92320</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473119</v>
+        <v>473100</v>
       </c>
       <c r="R16" t="n">
-        <v>6990938</v>
+        <v>6990917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,7 +2413,7 @@
         <v>129762625</v>
       </c>
       <c r="B17" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129762636</v>
       </c>
       <c r="B18" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>129762561</v>
       </c>
       <c r="B19" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>129762638</v>
       </c>
       <c r="B20" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>129762621</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -2144,41 +2144,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129762637</v>
+        <v>129762560</v>
       </c>
       <c r="B15" t="n">
-        <v>91598</v>
+        <v>92320</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2186,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473119</v>
+        <v>473100</v>
       </c>
       <c r="R15" t="n">
-        <v>6990938</v>
+        <v>6990917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,7 +2222,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,37 +2275,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762560</v>
+        <v>129762637</v>
       </c>
       <c r="B16" t="n">
-        <v>92320</v>
+        <v>91598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473100</v>
+        <v>473119</v>
       </c>
       <c r="R16" t="n">
-        <v>6990917</v>
+        <v>6990938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran i gammal granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762636</v>
+        <v>129762561</v>
       </c>
       <c r="B18" t="n">
-        <v>91598</v>
+        <v>92320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473139</v>
+        <v>473144</v>
       </c>
       <c r="R18" t="n">
-        <v>6990943</v>
+        <v>6991057</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I en granstubbe.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2673,32 +2673,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762561</v>
+        <v>129762636</v>
       </c>
       <c r="B19" t="n">
-        <v>92320</v>
+        <v>91598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473144</v>
+        <v>473139</v>
       </c>
       <c r="R19" t="n">
-        <v>6991057</v>
+        <v>6990943</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>I en granstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129488916</v>
+        <v>129486912</v>
       </c>
       <c r="B2" t="n">
-        <v>91595</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473088</v>
+        <v>473268</v>
       </c>
       <c r="R2" t="n">
-        <v>6990992</v>
+        <v>6991017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129488870</v>
+        <v>129488424</v>
       </c>
       <c r="B3" t="n">
-        <v>91372</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473103</v>
+        <v>473162</v>
       </c>
       <c r="R3" t="n">
-        <v>6991022</v>
+        <v>6991027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,49 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129487230</v>
+        <v>129488640</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473259</v>
+        <v>473136</v>
       </c>
       <c r="R4" t="n">
-        <v>6991004</v>
+        <v>6991010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,45 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129487778</v>
+        <v>129488916</v>
       </c>
       <c r="B5" t="n">
-        <v>92317</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473224</v>
+        <v>473088</v>
       </c>
       <c r="R5" t="n">
-        <v>6991067</v>
+        <v>6990992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129486912</v>
+        <v>129762635</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,16 +1132,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473268</v>
+        <v>473156</v>
       </c>
       <c r="R6" t="n">
-        <v>6991017</v>
+        <v>6990959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,22 +1175,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,63 +1194,96 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129487135</v>
+        <v>129762636</v>
       </c>
       <c r="B7" t="n">
-        <v>97661</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473259</v>
+        <v>473139</v>
       </c>
       <c r="R7" t="n">
-        <v>6991004</v>
+        <v>6990943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,22 +1310,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I en granstubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,28 +1329,54 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129488424</v>
+        <v>129762637</v>
       </c>
       <c r="B8" t="n">
-        <v>91595</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,16 +1402,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473162</v>
+        <v>473119</v>
       </c>
       <c r="R8" t="n">
-        <v>6991027</v>
+        <v>6990938</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,22 +1445,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,63 +1464,96 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129487063</v>
+        <v>129762638</v>
       </c>
       <c r="B9" t="n">
-        <v>91563</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473259</v>
+        <v>473089</v>
       </c>
       <c r="R9" t="n">
-        <v>6991004</v>
+        <v>6990979</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,22 +1580,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I 2 stående döda granar som står nära varann.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,72 +1599,96 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129488344</v>
+        <v>129762640</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillutloppet, Lillutloppet, Jmt</t>
+          <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473159</v>
+        <v>473215</v>
       </c>
       <c r="R10" t="n">
-        <v>6991024</v>
+        <v>6991103</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,22 +1715,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I en smal stående död gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,67 +1734,89 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129488378</v>
+        <v>129488870</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473156</v>
+        <v>473103</v>
       </c>
       <c r="R11" t="n">
-        <v>6991029</v>
+        <v>6991022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1735,12 +1858,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,45 +1885,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129488640</v>
+        <v>129487778</v>
       </c>
       <c r="B12" t="n">
-        <v>91595</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Haraån, Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473136</v>
+        <v>473224</v>
       </c>
       <c r="R12" t="n">
-        <v>6991010</v>
+        <v>6991067</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1965,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,32 +1992,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129762635</v>
+        <v>129762559</v>
       </c>
       <c r="B13" t="n">
-        <v>91635</v>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +2034,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473156</v>
+        <v>473216</v>
       </c>
       <c r="R13" t="n">
-        <v>6990959</v>
+        <v>6991032</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +2074,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I en stående död gran med full längd.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129762559</v>
+        <v>129762560</v>
       </c>
       <c r="B14" t="n">
-        <v>92357</v>
+        <v>92632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,11 +2157,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2051,10 +2165,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473216</v>
+        <v>473100</v>
       </c>
       <c r="R14" t="n">
-        <v>6991032</v>
+        <v>6990917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,7 +2205,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>I stambasen av en döende gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2258,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129762560</v>
+        <v>129762561</v>
       </c>
       <c r="B15" t="n">
-        <v>92357</v>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,7 +2288,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2182,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473100</v>
+        <v>473144</v>
       </c>
       <c r="R15" t="n">
-        <v>6990917</v>
+        <v>6991057</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2340,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran i gammal granskog.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,52 +2393,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129762637</v>
+        <v>129487063</v>
       </c>
       <c r="B16" t="n">
-        <v>91635</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473119</v>
+        <v>473259</v>
       </c>
       <c r="R16" t="n">
-        <v>6990938</v>
+        <v>6991004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,17 +2458,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,109 +2482,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129762625</v>
+        <v>129488378</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Haraån, Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473178</v>
+        <v>473156</v>
       </c>
       <c r="R17" t="n">
-        <v>6990958</v>
+        <v>6991029</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,17 +2569,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 53 plantor inom ca 1 m2 yta.</t>
+          <t>Tretåig hackspett hona</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,34 +2598,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129762636</v>
+        <v>129733684</v>
       </c>
       <c r="B18" t="n">
-        <v>91635</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,41 +2627,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473139</v>
+        <v>473270</v>
       </c>
       <c r="R18" t="n">
-        <v>6990943</v>
+        <v>6991065</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,17 +2697,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I en granstubbe.</t>
+          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,34 +2716,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2673,52 +2734,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762561</v>
+        <v>129487230</v>
       </c>
       <c r="B19" t="n">
-        <v>92357</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473144</v>
+        <v>473259</v>
       </c>
       <c r="R19" t="n">
-        <v>6991057</v>
+        <v>6991004</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,17 +2803,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I en stående död gran.</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2764,96 +2827,72 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762638</v>
+        <v>129488344</v>
       </c>
       <c r="B20" t="n">
-        <v>91635</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473089</v>
+        <v>473159</v>
       </c>
       <c r="R20" t="n">
-        <v>6990979</v>
+        <v>6991024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2880,17 +2919,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I 2 stående döda granar som står nära varann.</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2899,44 +2943,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2946,7 +2964,7 @@
         <v>129762621</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3068,6 +3086,241 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129762625</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Haraån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>473178</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6990958</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 53 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129487135</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>473259</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6991004</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48736-2025 artfynd.xlsx
+++ b/artfynd/A 48736-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129486912</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129488424</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129488640</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129488916</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762635</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762636</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762637</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1640,6 +1680,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762638</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1775,6 +1820,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762640</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1882,6 +1932,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129488870</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1989,6 +2044,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487778</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2124,6 +2184,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762559</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2255,6 +2320,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762560</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2390,6 +2460,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762561</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2497,6 +2572,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487063</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2613,6 +2693,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129488378</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2731,6 +2816,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733684</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2842,6 +2932,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487230</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2958,6 +3053,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129488344</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3086,6 +3186,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762621</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3214,6 +3319,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762625</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3321,8 +3431,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487135</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>